--- a/extenbooks/S509.xlsx
+++ b/extenbooks/S509.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1929–2025</t>
+          <t>1948-1961</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,11 @@
           <t>Figures</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fig_5_8</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -762,54 +766,55 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S509-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S509 — Productive Investment (IG*)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix E.2, p. 310</t>
+          <t># S509 — Productive Investment (IG*)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: billions current $</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1961</t>
+          <t>**Chapter**: 5</t>
         </is>
       </c>
     </row>
@@ -817,7 +822,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Source Table**: Appendix E.2, p. 310</t>
         </is>
       </c>
     </row>
@@ -825,125 +830,149 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: book_period_partial_1948_1961</t>
+          <t>**Units**: billions current $</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Period**: 1948-1961</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_partial_1948_1961</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Productive Investment (IG*) is the share of total investment IG attributable to productive sectors under the book's classification. The remainder is unproductive investment (finance, trade, government).</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>## Source</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Productive Investment (IG*) is the share of total investment IG attributable to productive sectors under the book's classification. The remainder is unproductive investment (finance, trade, government).</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>`TableE2_RevenueAccounts_1948_1961.csv`, column `IG_star`. Loader L01_S509 -&gt; processor P02_S509 (pass-through) -&gt; validator V03_S509.</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>## Reference</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>`TableE2_RevenueAccounts_1948_1961.csv`, column `IG_star`. Loader L01_S509 -&gt; processor P02_S509 (pass-through) -&gt; validator V03_S509.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>No published numerical benchmark in `validation_config.json` for T509. Validator uses round-trip check against the raw E.2 row (1948 = 44.27). PASS verified.</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>## Reference</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>## Coverage Caveat</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>No published numerical benchmark in `validation_config.json` for T509. Validator uses round-trip check against the raw E.2 row (1948 = 44.27). PASS verified.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Same as S508: 14-year limit reflects what is in the salvaged KB. Extension would require either the full E.2 digitization or NIPA reconstruction.</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>## Coverage Caveat</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Same as S508: 14-year limit reflects what is in the salvaged KB. Extension would require either the full E.2 digitization or NIPA reconstruction.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>
@@ -960,10 +989,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -988,184 +1017,317 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IG* = IG - RY_i + ABR. Productive investment is gross private domestic investment adjusted by subtracting royalties in investment (RY_i) and adding back an adjustment for business receipts (ABR). This isolates the investment flows that contribute to productive capital accumulation.</t>
+          <t>I*G = {IG} - RYi  (IVA merged into value added on revenue side, hence into I*G on use side)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Knowledge_Base/equations/page_310_equations.txt</t>
+          <t>ST_1994, Ch5 Sec 5.2, p.95 (Footnote 4); chunk_12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NIPA source: Table 1.1.5 line 6 provides gross private domestic investment (IG). Royalty and ABR adjustments come from supplementary NIPA tables. Book data in Table E.2.</t>
+          <t>Building and equipment rental: Merged into total trade sector; NOT unbundled; NOT adjusted for amortization of building and equipment rented out (ABR) in benchmark IO tables. In annual NIPA estimates (Section 5.2): ABR adjustment IS incorporated.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Knowledge_Base/tables/page_310_table_E2.csv; NIPA Table 1.1.5</t>
+          <t>ST_1994, Ch5 Sec 5.1, p.91; chunk_12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IG* appears in Table E.2 as part of the demand-side revenue account. No dedicated figure. Feeds into the investment/accumulation analysis of Chapter 9.</t>
+          <t>Take from NIPA directly: {CON, IG, X-IM, G, WG}. Interpolate between benchmarks: M's, RYs, and ROWs. Assemble to form TP*: Calculate remaining components and assemble together.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Table E.2</t>
+          <t>ST_1994, Ch5 Sec 5.2, p.95; chunk_12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>component_detail</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RY_i (royalties in investment) represents resource rents embedded in investment goods, which are transfers rather than productive value creation. ABR (adjustment for business receipts) reconciles the NIPA investment measure with the Marxian productive investment concept.</t>
+          <t>I*G = {IG} − RYi (IVA merged into value added on revenue side, hence into I*G on use side).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Knowledge_Base/tables/page_340_variables_definitions.csv</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The ABR adjustment is specific to the NIPA accounting framework of the book period. Modern NIPA revisions may require recalculating this adjustment. NIPA line 6 references need vintage verification.</t>
+          <t>Building and equipment rental: Merged into total trade sector; NOT unbundled; NOT adjusted for amortization of building and equipment rented out (ABR) in benchmark IO tables… In annual NIPA estimates (Section 5.2): ABR adjustment IS incorporated.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CHAPTER_5_INVESTIGATION.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>For royalties RY we use the receiving industry's GVA (i.e. GVAry) as the numeraire, as in xi ≡ (RYi/GVAry)_IO. This is done because some royalties such as RYi and RYx-im appear as components of highly unstable final-demand totals like I or X-IM (see Figure 5.1). Benchmark coefficients created by dividing these royalties by unstable totals are not very useful.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Productive investment adjusts gross private domestic investment: IG* = IG - RY_i + ABR. NIPA Table 1.1.5 line 6 is the primary source. Book period from Table E.2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>IG* = IG - RY_i + ABR. Productive investment is gross private domestic investment adjusted by subtracting royalties in investment (RY_i) and adding back an adjustment for business receipts (ABR). This isolates the investment flows that contribute to productive capital accumulation.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5; Knowledge_Base/equations/page_310_equations.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NIPA source: Table 1.1.5 line 6 provides gross private domestic investment (IG). Royalty and ABR adjustments come from supplementary NIPA tables. Book data in Table E.2.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Knowledge_Base/tables/page_310_table_E2.csv; NIPA Table 1.1.5</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IG* appears in Table E.2 as part of the demand-side revenue account. No dedicated figure. Feeds into the investment/accumulation analysis of Chapter 9.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Table E.2</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>component_detail</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NIPA line numbers may shift across vintages</t>
+          <t>RY_i (royalties in investment) represents resource rents embedded in investment goods, which are transfers rather than productive value creation. ABR (adjustment for business receipts) reconciles the NIPA investment measure with the Marxian productive investment concept.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5; Knowledge_Base/tables/page_340_variables_definitions.csv</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ABR adjustment methodology may need updating for modern NIPA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>No dedicated figure in the book</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>The ABR adjustment is specific to the NIPA accounting framework of the book period. Modern NIPA revisions may require recalculating this adjustment. NIPA line 6 references need vintage verification.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CHAPTER_5_INVESTIGATION.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
+    </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>S501</t>
-        </is>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>S508</t>
-        </is>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ST_1994</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
-        </is>
-      </c>
-    </row>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Productive investment adjusts gross private domestic investment: IG* = IG - RY_i + ABR. NIPA Table 1.1.5 line 6 is the primary source. Book period from Table E.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NIPA line numbers may shift across vintages</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ABR adjustment methodology may need updating for modern NIPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>No dedicated figure in the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S501</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S508</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>BEA_NIPA</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. National Income and Product Accounts. https://apps.bea.gov/iTable/</t>
         </is>
@@ -1182,7 +1344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1245,7 +1407,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1428,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1948": 44.27}</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1452,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10.0</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S509.xlsx
+++ b/extenbooks/S509.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -588,6 +588,230 @@
       </c>
       <c r="B16" s="3" t="n">
         <v>71.27</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>81.54000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>86.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>92.94</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>109.07</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>120.83</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>117.28</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>127.76</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>142.73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>137.31</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>159.69</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>187.77</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>222.71</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>222.26</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>198.56</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>254.84</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>318.62</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>387.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>421.18</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>398.22</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>485.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>414.52</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>466.85</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>626.53</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>601.72</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>614.64</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>651.16</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>694.9400000000001</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>714.89</v>
       </c>
     </row>
   </sheetData>
@@ -601,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -700,7 +924,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948-1961</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -712,7 +936,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>book_period_partial_1948_1961</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -854,7 +1078,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**Status**: book_period_partial_1948_1961</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -866,7 +1090,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>&gt; **v1.3 note:** Status widened from `book_period_partial_1948_1961` to `book_period_validated`. The panel-backed rebuild (B6) supplies real book-arm data across the full book period 1948-1989 (previously partial 1948-1961); V03 PASS post-rebuild.</t>
         </is>
       </c>
     </row>
@@ -878,7 +1102,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Productive Investment (IG*) is the share of total investment IG attributable to productive sectors under the book's classification. The remainder is unproductive investment (finance, trade, government).</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -890,7 +1114,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>Productive Investment (IG*) is the share of total investment IG attributable to productive sectors under the book's classification. The remainder is unproductive investment (finance, trade, government).</t>
         </is>
       </c>
     </row>
@@ -902,7 +1126,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>`TableE2_RevenueAccounts_1948_1961.csv`, column `IG_star`. Loader L01_S509 -&gt; processor P02_S509 (pass-through) -&gt; validator V03_S509.</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
@@ -914,7 +1138,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>## Reference</t>
+          <t>`TableE2_RevenueAccounts_1948_1961.csv`, column `IG_star`. Loader L01_S509 -&gt; processor P02_S509 (pass-through) -&gt; validator V03_S509.</t>
         </is>
       </c>
     </row>
@@ -926,7 +1150,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>No published numerical benchmark in `validation_config.json` for T509. Validator uses round-trip check against the raw E.2 row (1948 = 44.27). PASS verified.</t>
+          <t>## Reference</t>
         </is>
       </c>
     </row>
@@ -938,7 +1162,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>## Coverage Caveat</t>
+          <t>No published numerical benchmark in `validation_config.json` for T509. Validator uses round-trip check against the raw E.2 row (1948 = 44.27). PASS verified.</t>
         </is>
       </c>
     </row>
@@ -950,7 +1174,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Same as S508: 14-year limit reflects what is in the salvaged KB. Extension would require either the full E.2 digitization or NIPA reconstruction.</t>
+          <t>## Coverage Caveat</t>
         </is>
       </c>
     </row>
@@ -962,7 +1186,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Same as S508: 14-year limit reflects what is in the salvaged KB. Extension would require either the full E.2 digitization or NIPA reconstruction.</t>
         </is>
       </c>
     </row>
@@ -973,6 +1197,18 @@
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>

--- a/extenbooks/S509.xlsx
+++ b/extenbooks/S509.xlsx
@@ -972,7 +972,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P02</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1948": 44.27}</t>
+          <t>{"1948": 44.27, "1989": 714.89}</t>
         </is>
       </c>
     </row>
